--- a/ig/ch-term/ValueSet-ch-vacd-vaccines-vs.xlsx
+++ b/ig/ch-term/ValueSet-ch-vacd-vaccines-vs.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-15T10:47:47+00:00</t>
+    <t>2026-06-10T10:00:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
